--- a/BOM.xlsx
+++ b/BOM.xlsx
@@ -5,27 +5,22 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Blueprint\Split keyboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Blueprint\Key bored\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C341D90-2234-429F-A8F1-80C1AFDB1F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4208D565-D3BE-425E-8916-5ABC4C810B31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8446CAAF-3A29-4A0D-93C0-1FE92A49E7F8}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{47B9E601-5B08-4B73-A3DD-37C3AA3EEF9D}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="BOM" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="43">
   <si>
     <t>Name</t>
   </si>
@@ -33,9 +28,6 @@
     <t>Comment</t>
   </si>
   <si>
-    <t>Designator</t>
-  </si>
-  <si>
     <t>Footprint</t>
   </si>
   <si>
@@ -48,128 +40,125 @@
     <t>Links</t>
   </si>
   <si>
-    <t>D2,D31,D33,D18,D45,D25,D17,D32,D28,D39,D43,D3,D35,D19,D42,D27,D16,D30,D23,D40,D11,D13,D4,D24,D41,D9,D10,D20,D26,D15,D34,D22,D7,D36,D38,D8,D14,D37,D12,D21,D1,D5,D29,D46,D6,D44</t>
+    <t>Price (Not include shipping</t>
+  </si>
+  <si>
+    <t>CR0805F88063G</t>
+  </si>
+  <si>
+    <t>806k</t>
+  </si>
+  <si>
+    <t>R_0805_2012Metric</t>
+  </si>
+  <si>
+    <t>C101872</t>
+  </si>
+  <si>
+    <t>https://jlcpcb.com/partdetail/LIZElec-CR0805F88063G/C101872</t>
+  </si>
+  <si>
+    <t>Within PCB</t>
+  </si>
+  <si>
+    <t>1N4148W diode</t>
+  </si>
+  <si>
+    <t>1N4148W</t>
   </si>
   <si>
     <t>D_SOD-123</t>
   </si>
   <si>
-    <t>TP1,TP2</t>
+    <t>C81598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://jlcpcb.com/partdetail/ST_Semtech-1N4148W/C81598 </t>
   </si>
   <si>
     <t>TestPoint_Pad_D2.0mm</t>
   </si>
   <si>
-    <t>SW10,SW44,SW7,SW2,SW23,SW5,SW19,SW3,SW8,SW30,SW37,SW36,SW14,SW12,SW26,SW31,SW34,SW38,SW15,SW27,SW25,SW9,SW18,SW33,SW28,SW24,SW39,SW21,SW29,SW42,SW16,SW4,SW22,SW11,SW40,SW46,SW41,SW45,SW1,SW43,SW32,SW20,SW35,SW6,SW17,SW13</t>
+    <t>PCB from JLCPCB</t>
+  </si>
+  <si>
+    <t>Kalih hotswap sockets</t>
   </si>
   <si>
     <t>SW_MX_HS_CPG151101S11_1u</t>
   </si>
   <si>
-    <t>TP3,TP4</t>
-  </si>
-  <si>
-    <t>R_0805_2012Metric</t>
-  </si>
-  <si>
-    <t>806k</t>
-  </si>
-  <si>
-    <t>U1,U2</t>
+    <t>Not from JLC PCB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.aliexpress.us/item/3256809253442692.html </t>
+  </si>
+  <si>
+    <t>XIAO nRF52840 SMD</t>
   </si>
   <si>
     <t>modified-XIAO-nRF52840-SMD</t>
   </si>
   <si>
+    <t xml:space="preserve">https://www.aliexpress.us/item/3256806802639384.html </t>
+  </si>
+  <si>
+    <t>SK6812MINI - E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SK6812 </t>
+  </si>
+  <si>
     <t>MX_SK6812MINI-E_REV</t>
   </si>
   <si>
-    <t>J2,J1</t>
+    <t>Hand solder, not from JLC PCB</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.us/item/3256805061849599.html</t>
+  </si>
+  <si>
+    <t>JST connector</t>
   </si>
   <si>
     <t>JST_PH_S2B-PH-K_1x02_P2.00mm_Horizontal</t>
   </si>
   <si>
-    <t>Not from JLC PCB</t>
-  </si>
-  <si>
-    <t>XIAO nRF52840 SMD</t>
-  </si>
-  <si>
-    <t>Kalih hotswap sockets</t>
+    <t>https://www.aliexpress.us/item/3256804769340392.html</t>
   </si>
   <si>
     <t>MX switches</t>
   </si>
   <si>
-    <t>https://www.aliexpress.us/item/3256809253442692.html</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://www.aliexpress.us/item/3256805881801670.html </t>
   </si>
   <si>
     <t>Rechargable Lipo battery</t>
   </si>
   <si>
+    <t>3.7 V-100mAh-0.37W</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://www.aliexpress.us/item/3256805604531299.html </t>
   </si>
   <si>
-    <t>3.7 V-100mAh-0.37W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.aliexpress.us/item/3256806802639384.html </t>
-  </si>
-  <si>
-    <t>https://www.aliexpress.us/item/3256804769340392.html</t>
-  </si>
-  <si>
-    <t>1N4148W diode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://jlcpcb.com/partdetail/ST_Semtech-1N4148W/C81598 </t>
-  </si>
-  <si>
-    <t>C81598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://jlcpcb.com/partdetail/OPSCOOptoelectronics-SK6812MINIE/C5149201 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">C5149201 </t>
-  </si>
-  <si>
-    <t>1N4148W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SK6812 </t>
-  </si>
-  <si>
-    <t>SK6812MINI - E</t>
-  </si>
-  <si>
-    <t>JST connector</t>
-  </si>
-  <si>
-    <t>https://jlcpcb.com/partdetail/LIZElec-CR0805F88063G/C101872</t>
-  </si>
-  <si>
-    <t>C101872</t>
-  </si>
-  <si>
-    <t>CR0805F88063G</t>
-  </si>
-  <si>
-    <t>806k+8:9</t>
-  </si>
-  <si>
-    <t>R1,R2,R3,R4</t>
+    <t>Heat inserts</t>
+  </si>
+  <si>
+    <t>M3x5x4</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.us/p/shoppingcart/index.html</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+  </numFmts>
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -178,23 +167,315 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -202,21 +483,205 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="42">
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -527,17 +992,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{140FA6A7-89EB-4E1C-96E1-3C85C84ED53C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D5D0A64-455C-4D80-8B19-A414C3169553}">
   <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="19" customWidth="1"/>
-    <col min="2" max="2" width="15.90625" customWidth="1"/>
-    <col min="3" max="3" width="25.54296875" customWidth="1"/>
-    <col min="4" max="4" width="15.6328125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.6328125" customWidth="1"/>
-    <col min="7" max="7" width="31.54296875" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -549,7 +1006,7 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
@@ -562,200 +1019,212 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2">
+        <v>4</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3">
+        <v>46</v>
+      </c>
+      <c r="F3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="G4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1">
+        <v>35.71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6">
+        <v>46</v>
+      </c>
+      <c r="F6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="1">
+        <v>12.17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="1">
+        <v>17.96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8">
+        <v>46</v>
+      </c>
+      <c r="F8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="1">
+        <v>6.16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>32</v>
       </c>
-      <c r="B2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9" t="s">
         <v>34</v>
       </c>
-      <c r="F2">
-        <v>46</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="145" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4">
-        <v>46</v>
-      </c>
-      <c r="G4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" t="s">
-        <v>42</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7">
-        <v>2</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8">
-        <v>46</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9">
-        <v>2</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>31</v>
+      <c r="G9" s="1">
+        <v>1.6</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10">
+        <v>35</v>
+      </c>
+      <c r="D10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10">
         <v>46</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>26</v>
+      <c r="F10" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" s="1">
+        <v>8.0500000000000007</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11">
+        <v>38</v>
+      </c>
+      <c r="D11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11">
         <v>2</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>28</v>
+      <c r="F11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G11" s="1">
+        <v>7.01</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="G12" s="2"/>
+      <c r="A12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="1">
+        <v>2.63</v>
+      </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="G7" r:id="rId1" xr:uid="{2668E73B-C822-45C6-8D57-42FF0DE6DCF0}"/>
-    <hyperlink ref="G2" r:id="rId2" xr:uid="{289A9F41-7F44-4101-AF46-ED8983649FBD}"/>
-    <hyperlink ref="G6" r:id="rId3" xr:uid="{62AC3AE3-6CC9-454F-B3C0-9C4A11275932}"/>
-    <hyperlink ref="G10" r:id="rId4" display="https://www.aliexpress.us/item/3256805604531299.html " xr:uid="{3E4CC4DF-73AA-4FBE-A815-6129B63F41AD}"/>
-    <hyperlink ref="G11" r:id="rId5" display="https://www.aliexpress.us/item/3256806802639384.html " xr:uid="{84A34B67-633E-4499-A3C7-7E96F26F0DCC}"/>
-    <hyperlink ref="G9" r:id="rId6" display="https://jlcpcb.com/partdetail/LIZElec-CR0805F88063G/C101872" xr:uid="{B8393BD4-140F-4DB1-B43F-F27285F4086A}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>